--- a/data/Companies_reports/Hudbay Minerals Inc/Hudbay-2023-Integrated-Annual-Report-Performance-Data.xlsx
+++ b/data/Companies_reports/Hudbay Minerals Inc/Hudbay-2023-Integrated-Annual-Report-Performance-Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/canada_metal_sustainability_db/data/Companies_reports/Hudbay Minerals Inc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7934DDFB-6DA2-564A-8B6A-E184938E29F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04472410-8FD0-4534-863F-DE4FB200E045}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{7934DDFB-6DA2-564A-8B6A-E184938E29F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{054A906F-42D7-45B9-A01E-DC9B016B8B7E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10613,6 +10613,10 @@
       <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f>C4/C8</f>
+        <v>0.11420612813370473</v>
+      </c>
       <c r="B4" s="5" t="s">
         <v>197</v>
       </c>
@@ -10633,6 +10637,10 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f>C5/C8</f>
+        <v>0.88101870274572225</v>
+      </c>
       <c r="B5" s="5" t="s">
         <v>198</v>
       </c>
@@ -10653,6 +10661,10 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f>C6/C8</f>
+        <v>3.9793076004775172E-3</v>
+      </c>
       <c r="B6" s="5" t="s">
         <v>199</v>
       </c>
